--- a/public/templateFiles/YEAR_DEPT NAME_COMPETITVE EXAM.xlsx
+++ b/public/templateFiles/YEAR_DEPT NAME_COMPETITVE EXAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bce256ff79113794/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B271EFC-8ECA-438D-A794-6C32E716609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA2DD829-FAC2-4421-B442-8836B56DF395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,17 +446,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="63.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" customWidth="1"/>
+    <col min="8" max="8" width="63.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -468,7 +468,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -480,7 +480,7 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:9" ht="121.5">
+    <row r="3" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -506,22 +506,22 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
